--- a/dev_docs/Tetra数值表_26_6_4.xlsx
+++ b/dev_docs/Tetra数值表_26_6_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8035DB36-2004-408E-9235-BFF95C4C30D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7DA37F-7A5F-4564-8D79-70CF075ABC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="496">
   <si>
     <t>刀刃</t>
   </si>
@@ -2135,6 +2135,10 @@
   <si>
     <t>全属性+0.001</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>护甲穿透+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2411,12 +2415,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2425,6 +2423,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2756,10 +2760,10 @@
       <c r="T1" s="24" t="s">
         <v>317</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="U1" s="34" t="s">
         <v>268</v>
       </c>
-      <c r="V1" s="30"/>
+      <c r="V1" s="34"/>
     </row>
     <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="3" t="s">
@@ -2775,10 +2779,10 @@
         <v>0.4</v>
       </c>
       <c r="G2" s="9">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H2" s="9">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I2" s="13">
         <f t="shared" ref="I2:I7" si="0">SUM(E2:H2)</f>
@@ -2813,12 +2817,12 @@
       <c r="T2" s="27" t="s">
         <v>318</v>
       </c>
-      <c r="U2" s="30" t="s">
+      <c r="U2" s="34" t="s">
         <v>468</v>
       </c>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
     </row>
     <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D3" s="3" t="s">
@@ -2831,10 +2835,10 @@
         <v>0.1</v>
       </c>
       <c r="G3" s="9">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H3" s="9">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I3" s="13">
         <f t="shared" si="0"/>
@@ -2866,12 +2870,12 @@
       <c r="S3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="U3" s="30" t="s">
+      <c r="U3" s="34" t="s">
         <v>329</v>
       </c>
-      <c r="V3" s="31"/>
-      <c r="W3" s="31"/>
-      <c r="X3" s="31"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
     </row>
     <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C4" s="3" t="s">
@@ -2887,10 +2891,10 @@
         <v>0.25</v>
       </c>
       <c r="G4" s="9">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="H4" s="9">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="I4" s="13">
         <f>SUM(E4:H4)</f>
@@ -5811,8 +5815,8 @@
       <c r="P58" s="9">
         <v>6</v>
       </c>
-      <c r="Q58" s="9" t="s">
-        <v>118</v>
+      <c r="Q58" s="23" t="s">
+        <v>495</v>
       </c>
       <c r="R58" s="9" t="s">
         <v>182</v>
@@ -11159,7 +11163,7 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
-      <c r="U9" s="34" t="s">
+      <c r="U9" s="32" t="s">
         <v>477</v>
       </c>
     </row>
@@ -11221,7 +11225,7 @@
       <c r="S10" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="U10" s="35" t="s">
+      <c r="U10" s="33" t="s">
         <v>476</v>
       </c>
     </row>
@@ -11232,22 +11236,22 @@
       <c r="B11" s="3">
         <v>20</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="31" t="s">
         <v>483</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="30">
         <v>2</v>
       </c>
-      <c r="E11" s="33" t="s">
+      <c r="E11" s="31" t="s">
         <v>488</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="30">
         <v>6</v>
       </c>
-      <c r="G11" s="32">
+      <c r="G11" s="30">
         <v>6</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="30">
         <v>3</v>
       </c>
       <c r="I11" s="17">
@@ -11294,22 +11298,22 @@
       <c r="B12" s="3">
         <v>155</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="30" t="s">
         <v>369</v>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="30">
         <v>4</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="31" t="s">
         <v>480</v>
       </c>
-      <c r="F12" s="32">
+      <c r="F12" s="30">
         <v>40</v>
       </c>
-      <c r="G12" s="32">
+      <c r="G12" s="30">
         <v>20</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="30">
         <v>20</v>
       </c>
       <c r="I12" s="17">
@@ -11354,22 +11358,22 @@
       <c r="B13" s="3">
         <v>10</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="31" t="s">
         <v>486</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="30">
         <v>1</v>
       </c>
-      <c r="E13" s="33" t="s">
+      <c r="E13" s="31" t="s">
         <v>489</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="30">
         <v>3</v>
       </c>
-      <c r="G13" s="32">
+      <c r="G13" s="30">
         <v>1</v>
       </c>
-      <c r="H13" s="32">
+      <c r="H13" s="30">
         <v>1.5</v>
       </c>
       <c r="I13" s="17">
@@ -11414,22 +11418,22 @@
       <c r="B14" s="3">
         <v>15</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="31" t="s">
         <v>493</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="30">
         <v>2</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="E14" s="31" t="s">
         <v>492</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="30">
         <v>4</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="30">
         <v>2</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="30">
         <v>2.2000000000000002</v>
       </c>
       <c r="I14" s="17">

--- a/dev_docs/Tetra数值表_26_6_4.xlsx
+++ b/dev_docs/Tetra数值表_26_6_4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF7DA37F-7A5F-4564-8D79-70CF075ABC39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEEFF9F-B23B-4076-B1EF-49F5A1DDC471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3390" yWindow="3405" windowWidth="26430" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>

--- a/dev_docs/Tetra数值表_26_6_4.xlsx
+++ b/dev_docs/Tetra数值表_26_6_4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tony\AppData\Roaming\PrismLauncher\instances\SenDimsBanForges\minecraft\dev_docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\12044\AppData\Roaming\PrismLauncher\instances\SDBF\minecraft\dev_docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEEFF9F-B23B-4076-B1EF-49F5A1DDC471}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EC7408C-ACFF-461F-94FC-2D6A3F1FCE22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3390" yWindow="3405" windowWidth="26430" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="材料" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,22 @@
     <sheet name="护甲" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="501">
   <si>
     <t>刀刃</t>
   </si>
@@ -896,6 +907,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -982,6 +994,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -998,6 +1011,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1169,6 +1183,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -1792,6 +1807,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
+        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
@@ -2139,6 +2155,26 @@
   <si>
     <t>护甲穿透+1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>flammable_ingot</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2.1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>附魔：火焰保护I</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>附魔：火焰附加I</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>火焰伤害+4</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2159,6 +2195,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -2707,17 +2744,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:X163"/>
-  <sheetFormatPr defaultColWidth="16.625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="16.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="8.625" style="3" customWidth="1"/>
-    <col min="4" max="5" width="16.625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="8.625" style="3" customWidth="1"/>
-    <col min="7" max="16" width="12.625" style="3" customWidth="1"/>
-    <col min="17" max="19" width="15.625" style="3" customWidth="1"/>
-    <col min="20" max="16384" width="16.625" style="3"/>
+    <col min="1" max="3" width="8.6640625" style="3" customWidth="1"/>
+    <col min="4" max="5" width="16.6640625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" style="3" customWidth="1"/>
+    <col min="7" max="16" width="12.6640625" style="3" customWidth="1"/>
+    <col min="17" max="19" width="15.6640625" style="3" customWidth="1"/>
+    <col min="20" max="16384" width="16.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2765,7 +2802,7 @@
       </c>
       <c r="V1" s="34"/>
     </row>
-    <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
@@ -2824,7 +2861,7 @@
       <c r="W2" s="34"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
@@ -2877,7 +2914,7 @@
       <c r="W3" s="35"/>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
@@ -2919,7 +2956,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
@@ -2949,7 +2986,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
@@ -2986,7 +3023,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
@@ -3019,7 +3056,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F8" s="3" t="s">
         <v>29</v>
       </c>
@@ -3033,7 +3070,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F9" s="3" t="s">
         <v>30</v>
       </c>
@@ -3050,7 +3087,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -3115,7 +3152,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>5</v>
       </c>
@@ -3175,7 +3212,7 @@
       <c r="R11" s="9"/>
       <c r="S11" s="9"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="12" t="s">
         <v>46</v>
       </c>
@@ -3227,7 +3264,7 @@
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="12" t="s">
         <v>46</v>
       </c>
@@ -3281,7 +3318,7 @@
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>6</v>
       </c>
@@ -3341,7 +3378,7 @@
       <c r="R14" s="9"/>
       <c r="S14" s="9"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="5" t="s">
         <v>57</v>
       </c>
@@ -3395,7 +3432,7 @@
       <c r="R15" s="9"/>
       <c r="S15" s="9"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>8</v>
       </c>
@@ -3455,7 +3492,7 @@
       <c r="R16" s="9"/>
       <c r="S16" s="9"/>
     </row>
-    <row r="17" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="12" t="s">
         <v>63</v>
       </c>
@@ -3509,7 +3546,7 @@
       <c r="R17" s="9"/>
       <c r="S17" s="9"/>
     </row>
-    <row r="18" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>9</v>
       </c>
@@ -3569,7 +3606,7 @@
       <c r="R18" s="9"/>
       <c r="S18" s="9"/>
     </row>
-    <row r="19" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>4</v>
       </c>
@@ -3627,7 +3664,7 @@
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
     </row>
-    <row r="20" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="12" t="s">
         <v>73</v>
       </c>
@@ -3679,7 +3716,7 @@
       <c r="R20" s="9"/>
       <c r="S20" s="9"/>
     </row>
-    <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>5</v>
       </c>
@@ -3738,7 +3775,7 @@
       <c r="S21" s="9"/>
       <c r="U21" s="24"/>
     </row>
-    <row r="22" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
         <v>78</v>
       </c>
@@ -3791,7 +3828,7 @@
       <c r="S22" s="9"/>
       <c r="W22" s="24"/>
     </row>
-    <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="5" t="s">
         <v>78</v>
       </c>
@@ -3843,7 +3880,7 @@
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
     </row>
-    <row r="24" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>6</v>
       </c>
@@ -3903,7 +3940,7 @@
       </c>
       <c r="S24" s="9"/>
     </row>
-    <row r="25" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="12" t="s">
         <v>83</v>
       </c>
@@ -3956,7 +3993,7 @@
       <c r="S25" s="9"/>
       <c r="U25" s="24"/>
     </row>
-    <row r="26" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="12" t="s">
         <v>83</v>
       </c>
@@ -4011,7 +4048,7 @@
       <c r="S26" s="9"/>
       <c r="U26" s="24"/>
     </row>
-    <row r="27" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>8</v>
       </c>
@@ -4069,7 +4106,7 @@
       <c r="R27" s="9"/>
       <c r="S27" s="9"/>
     </row>
-    <row r="28" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="5" t="s">
         <v>91</v>
       </c>
@@ -4121,7 +4158,7 @@
       <c r="R28" s="9"/>
       <c r="S28" s="9"/>
     </row>
-    <row r="29" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="5" t="s">
         <v>91</v>
       </c>
@@ -4173,7 +4210,7 @@
       <c r="R29" s="9"/>
       <c r="S29" s="9"/>
     </row>
-    <row r="30" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>9</v>
       </c>
@@ -4234,7 +4271,7 @@
       <c r="S30" s="9"/>
       <c r="U30" s="24"/>
     </row>
-    <row r="31" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="12" t="s">
         <v>96</v>
       </c>
@@ -4289,7 +4326,7 @@
       <c r="S31" s="9"/>
       <c r="U31" s="24"/>
     </row>
-    <row r="32" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>8</v>
       </c>
@@ -4349,7 +4386,7 @@
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
     </row>
-    <row r="33" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="5" t="s">
         <v>100</v>
       </c>
@@ -4403,7 +4440,7 @@
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
     </row>
-    <row r="34" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="5" t="s">
         <v>100</v>
       </c>
@@ -4458,7 +4495,7 @@
       <c r="S34" s="9"/>
       <c r="U34" s="24"/>
     </row>
-    <row r="35" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>9</v>
       </c>
@@ -4521,7 +4558,7 @@
       <c r="S35" s="9"/>
       <c r="U35" s="24"/>
     </row>
-    <row r="36" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="12" t="s">
         <v>109</v>
       </c>
@@ -4575,7 +4612,7 @@
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
     </row>
-    <row r="37" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C37" s="12" t="s">
         <v>109</v>
       </c>
@@ -4629,7 +4666,7 @@
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
     </row>
-    <row r="38" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>10</v>
       </c>
@@ -4689,7 +4726,7 @@
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
     </row>
-    <row r="39" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="5" t="s">
         <v>119</v>
       </c>
@@ -4743,7 +4780,7 @@
       <c r="R39" s="9"/>
       <c r="S39" s="9"/>
     </row>
-    <row r="40" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="5" t="s">
         <v>119</v>
       </c>
@@ -4798,7 +4835,7 @@
       <c r="S40" s="9"/>
       <c r="U40" s="24"/>
     </row>
-    <row r="41" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>11</v>
       </c>
@@ -4858,7 +4895,7 @@
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
     </row>
-    <row r="42" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="12" t="s">
         <v>127</v>
       </c>
@@ -4915,7 +4952,7 @@
       <c r="S42" s="9"/>
       <c r="U42" s="24"/>
     </row>
-    <row r="43" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>13</v>
       </c>
@@ -4976,7 +5013,7 @@
       <c r="S43" s="9"/>
       <c r="W43" s="24"/>
     </row>
-    <row r="44" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="5" t="s">
         <v>133</v>
       </c>
@@ -5031,7 +5068,7 @@
       <c r="S44" s="9"/>
       <c r="U44" s="24"/>
     </row>
-    <row r="45" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" s="5" t="s">
         <v>133</v>
       </c>
@@ -5085,7 +5122,7 @@
       <c r="R45" s="9"/>
       <c r="S45" s="9"/>
     </row>
-    <row r="46" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="5" t="s">
         <v>133</v>
       </c>
@@ -5139,7 +5176,7 @@
       <c r="R46" s="9"/>
       <c r="S46" s="9"/>
     </row>
-    <row r="47" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>14</v>
       </c>
@@ -5199,7 +5236,7 @@
       <c r="R47" s="9"/>
       <c r="S47" s="9"/>
     </row>
-    <row r="48" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="12" t="s">
         <v>143</v>
       </c>
@@ -5254,7 +5291,7 @@
       <c r="S48" s="9"/>
       <c r="U48" s="24"/>
     </row>
-    <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>16</v>
       </c>
@@ -5316,7 +5353,7 @@
       </c>
       <c r="S49" s="9"/>
     </row>
-    <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C50" s="5" t="s">
         <v>149</v>
       </c>
@@ -5372,7 +5409,7 @@
       </c>
       <c r="S50" s="9"/>
     </row>
-    <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C51" s="5" t="s">
         <v>149</v>
       </c>
@@ -5426,7 +5463,7 @@
       <c r="R51" s="9"/>
       <c r="S51" s="9"/>
     </row>
-    <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C52" s="5" t="s">
         <v>149</v>
       </c>
@@ -5480,7 +5517,7 @@
       <c r="R52" s="9"/>
       <c r="S52" s="9"/>
     </row>
-    <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>19</v>
       </c>
@@ -5540,7 +5577,7 @@
       <c r="R53" s="9"/>
       <c r="S53" s="9"/>
     </row>
-    <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C54" s="12" t="s">
         <v>163</v>
       </c>
@@ -5595,7 +5632,7 @@
       <c r="S54" s="9"/>
       <c r="U54" s="24"/>
     </row>
-    <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C55" s="12" t="s">
         <v>163</v>
       </c>
@@ -5651,7 +5688,7 @@
       </c>
       <c r="S55" s="9"/>
     </row>
-    <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C56" s="5" t="s">
         <v>173</v>
       </c>
@@ -5705,7 +5742,7 @@
       <c r="R56" s="9"/>
       <c r="S56" s="9"/>
     </row>
-    <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C57" s="5" t="s">
         <v>173</v>
       </c>
@@ -5761,7 +5798,7 @@
       </c>
       <c r="S57" s="9"/>
     </row>
-    <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
         <v>22</v>
       </c>
@@ -5826,7 +5863,7 @@
       </c>
       <c r="U58" s="24"/>
     </row>
-    <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
         <v>14</v>
       </c>
@@ -5886,7 +5923,7 @@
       <c r="R59" s="9"/>
       <c r="S59" s="9"/>
     </row>
-    <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="5" t="s">
         <v>186</v>
       </c>
@@ -5942,7 +5979,7 @@
       </c>
       <c r="S60" s="9"/>
     </row>
-    <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
         <v>24</v>
       </c>
@@ -6002,7 +6039,7 @@
       <c r="R61" s="9"/>
       <c r="S61" s="9"/>
     </row>
-    <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="25" t="s">
         <v>288</v>
       </c>
@@ -6059,7 +6096,7 @@
       <c r="S62" s="9"/>
       <c r="U62" s="24"/>
     </row>
-    <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
         <v>24</v>
       </c>
@@ -6124,7 +6161,7 @@
       </c>
       <c r="U63" s="24"/>
     </row>
-    <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>29</v>
       </c>
@@ -6184,7 +6221,7 @@
       <c r="R64" s="9"/>
       <c r="S64" s="9"/>
     </row>
-    <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="5" t="s">
         <v>197</v>
       </c>
@@ -6238,7 +6275,7 @@
       <c r="R65" s="9"/>
       <c r="S65" s="9"/>
     </row>
-    <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="5" t="s">
         <v>197</v>
       </c>
@@ -6292,7 +6329,7 @@
       <c r="R66" s="9"/>
       <c r="S66" s="9"/>
     </row>
-    <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="5" t="s">
         <v>197</v>
       </c>
@@ -6349,7 +6386,7 @@
       <c r="S67" s="9"/>
       <c r="U67" s="24"/>
     </row>
-    <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
         <v>35</v>
       </c>
@@ -6409,7 +6446,7 @@
       <c r="R68" s="9"/>
       <c r="S68" s="9"/>
     </row>
-    <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="12" t="s">
         <v>208</v>
       </c>
@@ -6463,7 +6500,7 @@
       <c r="R69" s="9"/>
       <c r="S69" s="9"/>
     </row>
-    <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
         <v>40</v>
       </c>
@@ -6525,7 +6562,7 @@
       </c>
       <c r="S70" s="9"/>
     </row>
-    <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="5" t="s">
         <v>219</v>
       </c>
@@ -6584,7 +6621,7 @@
       </c>
       <c r="U71" s="24"/>
     </row>
-    <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="5" t="s">
         <v>219</v>
       </c>
@@ -6646,7 +6683,7 @@
       </c>
       <c r="U72" s="24"/>
     </row>
-    <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
         <v>40</v>
       </c>
@@ -6709,7 +6746,7 @@
       <c r="S73" s="9"/>
       <c r="U73" s="24"/>
     </row>
-    <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="12" t="s">
         <v>225</v>
       </c>
@@ -6765,7 +6802,7 @@
       </c>
       <c r="S74" s="9"/>
     </row>
-    <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="12" t="s">
         <v>225</v>
       </c>
@@ -6822,7 +6859,7 @@
       <c r="S75" s="9"/>
       <c r="U75" s="24"/>
     </row>
-    <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="12" t="s">
         <v>225</v>
       </c>
@@ -6879,7 +6916,7 @@
       <c r="S76" s="9"/>
       <c r="U76" s="24"/>
     </row>
-    <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
         <v>50</v>
       </c>
@@ -6940,7 +6977,7 @@
       <c r="S77" s="9"/>
       <c r="U77" s="24"/>
     </row>
-    <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="5" t="s">
         <v>228</v>
       </c>
@@ -6996,7 +7033,7 @@
       </c>
       <c r="S78" s="9"/>
     </row>
-    <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C79" s="5" t="s">
         <v>228</v>
       </c>
@@ -7051,7 +7088,7 @@
       <c r="S79" s="9"/>
       <c r="U79" s="24"/>
     </row>
-    <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="5" t="s">
         <v>228</v>
       </c>
@@ -7106,7 +7143,7 @@
       <c r="S80" s="9"/>
       <c r="U80" s="24"/>
     </row>
-    <row r="81" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C81" s="5" t="s">
         <v>228</v>
       </c>
@@ -7163,7 +7200,7 @@
       <c r="S81" s="9"/>
       <c r="U81" s="24"/>
     </row>
-    <row r="82" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
         <v>60</v>
       </c>
@@ -7225,7 +7262,7 @@
       </c>
       <c r="S82" s="9"/>
     </row>
-    <row r="83" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C83" s="12" t="s">
         <v>322</v>
       </c>
@@ -7281,7 +7318,7 @@
       </c>
       <c r="S83" s="9"/>
     </row>
-    <row r="84" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C84" s="12" t="s">
         <v>322</v>
       </c>
@@ -7337,7 +7374,7 @@
       </c>
       <c r="S84" s="9"/>
     </row>
-    <row r="85" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C85" s="12" t="s">
         <v>294</v>
       </c>
@@ -7394,7 +7431,7 @@
       <c r="S85" s="9"/>
       <c r="U85" s="24"/>
     </row>
-    <row r="86" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C86" s="12" t="s">
         <v>294</v>
       </c>
@@ -7451,7 +7488,7 @@
       <c r="S86" s="9"/>
       <c r="U86" s="24"/>
     </row>
-    <row r="87" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C87" s="12" t="s">
         <v>294</v>
       </c>
@@ -7510,7 +7547,7 @@
       </c>
       <c r="U87" s="24"/>
     </row>
-    <row r="88" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="12" t="s">
         <v>322</v>
       </c>
@@ -7565,7 +7602,7 @@
       <c r="S88" s="23"/>
       <c r="U88" s="24"/>
     </row>
-    <row r="89" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
         <v>70</v>
       </c>
@@ -7633,7 +7670,7 @@
       </c>
       <c r="U89" s="24"/>
     </row>
-    <row r="90" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="5" t="s">
         <v>234</v>
       </c>
@@ -7692,7 +7729,7 @@
       </c>
       <c r="U90" s="24"/>
     </row>
-    <row r="91" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="5" t="s">
         <v>296</v>
       </c>
@@ -7749,7 +7786,7 @@
       <c r="S91" s="23"/>
       <c r="U91" s="24"/>
     </row>
-    <row r="92" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
         <v>80</v>
       </c>
@@ -7815,7 +7852,7 @@
       <c r="U92" s="24"/>
       <c r="W92" s="24"/>
     </row>
-    <row r="93" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C93" s="12" t="s">
         <v>324</v>
       </c>
@@ -7874,7 +7911,7 @@
       </c>
       <c r="U93" s="24"/>
     </row>
-    <row r="94" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C94" s="12" t="s">
         <v>239</v>
       </c>
@@ -7933,7 +7970,7 @@
       </c>
       <c r="U94" s="24"/>
     </row>
-    <row r="95" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
         <v>60</v>
       </c>
@@ -7998,7 +8035,7 @@
       </c>
       <c r="U95" s="24"/>
     </row>
-    <row r="96" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
         <v>75</v>
       </c>
@@ -8066,7 +8103,7 @@
       </c>
       <c r="U96" s="24"/>
     </row>
-    <row r="97" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C97" s="12" t="s">
         <v>249</v>
       </c>
@@ -8125,7 +8162,7 @@
       </c>
       <c r="U97" s="24"/>
     </row>
-    <row r="98" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="24" t="s">
         <v>384</v>
       </c>
@@ -8191,7 +8228,7 @@
       </c>
       <c r="W98" s="24"/>
     </row>
-    <row r="99" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
         <v>105</v>
       </c>
@@ -8257,7 +8294,7 @@
       </c>
       <c r="W99" s="24"/>
     </row>
-    <row r="100" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C100" s="12" t="s">
         <v>371</v>
       </c>
@@ -8317,7 +8354,7 @@
       </c>
       <c r="W100" s="24"/>
     </row>
-    <row r="101" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C101" s="12" t="s">
         <v>371</v>
       </c>
@@ -8375,7 +8412,7 @@
       <c r="T101" s="23"/>
       <c r="W101" s="24"/>
     </row>
-    <row r="102" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C102" s="12" t="s">
         <v>371</v>
       </c>
@@ -8435,7 +8472,7 @@
       <c r="T102" s="23"/>
       <c r="W102" s="24"/>
     </row>
-    <row r="103" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
         <v>120</v>
       </c>
@@ -8501,7 +8538,7 @@
       </c>
       <c r="W103" s="24"/>
     </row>
-    <row r="104" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C104" s="5" t="s">
         <v>372</v>
       </c>
@@ -8561,7 +8598,7 @@
       <c r="T104" s="24"/>
       <c r="W104" s="24"/>
     </row>
-    <row r="105" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
         <v>135</v>
       </c>
@@ -8626,7 +8663,7 @@
       </c>
       <c r="W105" s="24"/>
     </row>
-    <row r="106" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
         <v>165</v>
       </c>
@@ -8696,7 +8733,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="107" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C107" s="5" t="s">
         <v>373</v>
       </c>
@@ -8756,7 +8793,7 @@
       <c r="T107" s="24"/>
       <c r="W107" s="24"/>
     </row>
-    <row r="108" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="5" t="s">
         <v>373</v>
       </c>
@@ -8824,7 +8861,7 @@
       </c>
       <c r="W108" s="24"/>
     </row>
-    <row r="109" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
         <v>180</v>
       </c>
@@ -8889,7 +8926,7 @@
       </c>
       <c r="W109" s="24"/>
     </row>
-    <row r="110" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
         <v>190</v>
       </c>
@@ -8954,7 +8991,7 @@
       </c>
       <c r="W110" s="24"/>
     </row>
-    <row r="111" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
         <v>210</v>
       </c>
@@ -9019,7 +9056,7 @@
       </c>
       <c r="W111" s="24"/>
     </row>
-    <row r="112" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
         <v>230</v>
       </c>
@@ -9087,7 +9124,7 @@
       </c>
       <c r="W112" s="24"/>
     </row>
-    <row r="113" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C113" s="5" t="s">
         <v>375</v>
       </c>
@@ -9149,7 +9186,7 @@
       </c>
       <c r="W113" s="24"/>
     </row>
-    <row r="114" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C114" s="5" t="s">
         <v>375</v>
       </c>
@@ -9208,7 +9245,7 @@
       </c>
       <c r="W114" s="24"/>
     </row>
-    <row r="115" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
         <v>250</v>
       </c>
@@ -9273,7 +9310,7 @@
       </c>
       <c r="W115" s="24"/>
     </row>
-    <row r="116" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C116" s="9"/>
       <c r="D116" s="9"/>
       <c r="E116" s="9"/>
@@ -9307,7 +9344,7 @@
       <c r="R116" s="9"/>
       <c r="S116" s="9"/>
     </row>
-    <row r="117" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C117" s="9"/>
       <c r="D117" s="9"/>
       <c r="E117" s="9"/>
@@ -9341,7 +9378,7 @@
       <c r="R117" s="9"/>
       <c r="S117" s="9"/>
     </row>
-    <row r="118" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C118" s="9"/>
       <c r="D118" s="9"/>
       <c r="E118" s="9"/>
@@ -9375,7 +9412,7 @@
       <c r="R118" s="9"/>
       <c r="S118" s="9"/>
     </row>
-    <row r="119" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C119" s="9"/>
       <c r="D119" s="9"/>
       <c r="E119" s="9"/>
@@ -9409,7 +9446,7 @@
       <c r="R119" s="9"/>
       <c r="S119" s="9"/>
     </row>
-    <row r="120" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C120" s="9"/>
       <c r="D120" s="9"/>
       <c r="E120" s="9"/>
@@ -9443,7 +9480,7 @@
       <c r="R120" s="9"/>
       <c r="S120" s="9"/>
     </row>
-    <row r="121" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C121" s="9"/>
       <c r="D121" s="9"/>
       <c r="E121" s="9"/>
@@ -9477,7 +9514,7 @@
       <c r="R121" s="9"/>
       <c r="S121" s="9"/>
     </row>
-    <row r="122" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C122" s="9"/>
       <c r="D122" s="9"/>
       <c r="E122" s="9"/>
@@ -9511,7 +9548,7 @@
       <c r="R122" s="9"/>
       <c r="S122" s="9"/>
     </row>
-    <row r="123" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="9"/>
       <c r="D123" s="9"/>
       <c r="E123" s="9"/>
@@ -9545,7 +9582,7 @@
       <c r="R123" s="9"/>
       <c r="S123" s="9"/>
     </row>
-    <row r="124" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C124" s="9"/>
       <c r="D124" s="9"/>
       <c r="E124" s="9"/>
@@ -9579,7 +9616,7 @@
       <c r="R124" s="9"/>
       <c r="S124" s="9"/>
     </row>
-    <row r="125" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="9"/>
       <c r="D125" s="9"/>
       <c r="E125" s="9"/>
@@ -9613,7 +9650,7 @@
       <c r="R125" s="9"/>
       <c r="S125" s="9"/>
     </row>
-    <row r="126" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="9"/>
       <c r="D126" s="9"/>
       <c r="E126" s="9"/>
@@ -9647,7 +9684,7 @@
       <c r="R126" s="9"/>
       <c r="S126" s="9"/>
     </row>
-    <row r="127" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C127" s="9"/>
       <c r="D127" s="9"/>
       <c r="E127" s="9"/>
@@ -9681,7 +9718,7 @@
       <c r="R127" s="9"/>
       <c r="S127" s="9"/>
     </row>
-    <row r="128" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C128" s="9"/>
       <c r="D128" s="9"/>
       <c r="E128" s="9"/>
@@ -9715,7 +9752,7 @@
       <c r="R128" s="9"/>
       <c r="S128" s="9"/>
     </row>
-    <row r="129" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C129" s="9"/>
       <c r="D129" s="9"/>
       <c r="E129" s="9"/>
@@ -9749,7 +9786,7 @@
       <c r="R129" s="9"/>
       <c r="S129" s="9"/>
     </row>
-    <row r="130" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C130" s="9"/>
       <c r="D130" s="9"/>
       <c r="E130" s="9"/>
@@ -9783,7 +9820,7 @@
       <c r="R130" s="9"/>
       <c r="S130" s="9"/>
     </row>
-    <row r="131" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="9"/>
       <c r="D131" s="9"/>
       <c r="E131" s="9"/>
@@ -9817,7 +9854,7 @@
       <c r="R131" s="9"/>
       <c r="S131" s="9"/>
     </row>
-    <row r="132" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C132" s="9"/>
       <c r="D132" s="9"/>
       <c r="E132" s="9"/>
@@ -9851,7 +9888,7 @@
       <c r="R132" s="9"/>
       <c r="S132" s="9"/>
     </row>
-    <row r="133" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C133" s="9"/>
       <c r="D133" s="9"/>
       <c r="E133" s="9"/>
@@ -9885,7 +9922,7 @@
       <c r="R133" s="9"/>
       <c r="S133" s="9"/>
     </row>
-    <row r="134" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C134" s="9"/>
       <c r="D134" s="9"/>
       <c r="E134" s="9"/>
@@ -9919,7 +9956,7 @@
       <c r="R134" s="9"/>
       <c r="S134" s="9"/>
     </row>
-    <row r="135" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C135" s="9"/>
       <c r="D135" s="9"/>
       <c r="E135" s="9"/>
@@ -9953,7 +9990,7 @@
       <c r="R135" s="9"/>
       <c r="S135" s="9"/>
     </row>
-    <row r="136" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C136" s="9"/>
       <c r="D136" s="9"/>
       <c r="E136" s="9"/>
@@ -9987,7 +10024,7 @@
       <c r="R136" s="9"/>
       <c r="S136" s="9"/>
     </row>
-    <row r="137" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="9"/>
       <c r="D137" s="9"/>
       <c r="E137" s="9"/>
@@ -10021,7 +10058,7 @@
       <c r="R137" s="9"/>
       <c r="S137" s="9"/>
     </row>
-    <row r="138" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C138" s="9"/>
       <c r="D138" s="9"/>
       <c r="E138" s="9"/>
@@ -10055,7 +10092,7 @@
       <c r="R138" s="9"/>
       <c r="S138" s="9"/>
     </row>
-    <row r="139" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C139" s="9"/>
       <c r="D139" s="9"/>
       <c r="E139" s="9"/>
@@ -10089,7 +10126,7 @@
       <c r="R139" s="9"/>
       <c r="S139" s="9"/>
     </row>
-    <row r="140" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C140" s="9"/>
       <c r="D140" s="9"/>
       <c r="E140" s="9"/>
@@ -10123,7 +10160,7 @@
       <c r="R140" s="9"/>
       <c r="S140" s="9"/>
     </row>
-    <row r="141" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C141" s="9"/>
       <c r="D141" s="9"/>
       <c r="E141" s="9"/>
@@ -10157,7 +10194,7 @@
       <c r="R141" s="9"/>
       <c r="S141" s="9"/>
     </row>
-    <row r="142" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C142" s="9"/>
       <c r="D142" s="9"/>
       <c r="E142" s="9"/>
@@ -10191,7 +10228,7 @@
       <c r="R142" s="9"/>
       <c r="S142" s="9"/>
     </row>
-    <row r="143" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C143" s="9"/>
       <c r="D143" s="9"/>
       <c r="E143" s="9"/>
@@ -10225,7 +10262,7 @@
       <c r="R143" s="9"/>
       <c r="S143" s="9"/>
     </row>
-    <row r="144" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C144" s="9"/>
       <c r="D144" s="9"/>
       <c r="E144" s="9"/>
@@ -10259,7 +10296,7 @@
       <c r="R144" s="9"/>
       <c r="S144" s="9"/>
     </row>
-    <row r="145" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C145" s="9"/>
       <c r="D145" s="9"/>
       <c r="E145" s="9"/>
@@ -10293,7 +10330,7 @@
       <c r="R145" s="9"/>
       <c r="S145" s="9"/>
     </row>
-    <row r="146" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="9"/>
       <c r="D146" s="9"/>
       <c r="E146" s="9"/>
@@ -10327,7 +10364,7 @@
       <c r="R146" s="9"/>
       <c r="S146" s="9"/>
     </row>
-    <row r="147" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C147" s="9"/>
       <c r="D147" s="9"/>
       <c r="E147" s="9"/>
@@ -10361,7 +10398,7 @@
       <c r="R147" s="9"/>
       <c r="S147" s="9"/>
     </row>
-    <row r="148" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C148" s="9"/>
       <c r="D148" s="9"/>
       <c r="E148" s="9"/>
@@ -10395,7 +10432,7 @@
       <c r="R148" s="9"/>
       <c r="S148" s="9"/>
     </row>
-    <row r="149" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C149" s="9"/>
       <c r="D149" s="9"/>
       <c r="E149" s="9"/>
@@ -10429,7 +10466,7 @@
       <c r="R149" s="9"/>
       <c r="S149" s="9"/>
     </row>
-    <row r="150" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C150" s="9"/>
       <c r="D150" s="9"/>
       <c r="E150" s="9"/>
@@ -10463,7 +10500,7 @@
       <c r="R150" s="9"/>
       <c r="S150" s="9"/>
     </row>
-    <row r="151" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C151" s="9"/>
       <c r="D151" s="9"/>
       <c r="E151" s="9"/>
@@ -10497,7 +10534,7 @@
       <c r="R151" s="9"/>
       <c r="S151" s="9"/>
     </row>
-    <row r="152" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C152" s="9"/>
       <c r="D152" s="9"/>
       <c r="E152" s="9"/>
@@ -10531,7 +10568,7 @@
       <c r="R152" s="9"/>
       <c r="S152" s="9"/>
     </row>
-    <row r="153" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C153" s="9"/>
       <c r="D153" s="9"/>
       <c r="E153" s="9"/>
@@ -10565,7 +10602,7 @@
       <c r="R153" s="9"/>
       <c r="S153" s="9"/>
     </row>
-    <row r="154" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C154" s="9"/>
       <c r="D154" s="9"/>
       <c r="E154" s="9"/>
@@ -10599,7 +10636,7 @@
       <c r="R154" s="9"/>
       <c r="S154" s="9"/>
     </row>
-    <row r="155" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C155" s="9"/>
       <c r="D155" s="9"/>
       <c r="E155" s="9"/>
@@ -10633,7 +10670,7 @@
       <c r="R155" s="9"/>
       <c r="S155" s="9"/>
     </row>
-    <row r="156" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C156" s="9"/>
       <c r="D156" s="9"/>
       <c r="E156" s="9"/>
@@ -10667,7 +10704,7 @@
       <c r="R156" s="9"/>
       <c r="S156" s="9"/>
     </row>
-    <row r="157" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C157" s="9"/>
       <c r="D157" s="9"/>
       <c r="E157" s="9"/>
@@ -10701,7 +10738,7 @@
       <c r="R157" s="9"/>
       <c r="S157" s="9"/>
     </row>
-    <row r="158" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C158" s="9"/>
       <c r="D158" s="9"/>
       <c r="E158" s="9"/>
@@ -10735,7 +10772,7 @@
       <c r="R158" s="9"/>
       <c r="S158" s="9"/>
     </row>
-    <row r="159" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C159" s="9"/>
       <c r="D159" s="9"/>
       <c r="E159" s="9"/>
@@ -10769,7 +10806,7 @@
       <c r="R159" s="9"/>
       <c r="S159" s="9"/>
     </row>
-    <row r="160" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C160" s="9"/>
       <c r="D160" s="9"/>
       <c r="E160" s="9"/>
@@ -10803,7 +10840,7 @@
       <c r="R160" s="9"/>
       <c r="S160" s="9"/>
     </row>
-    <row r="161" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C161" s="9"/>
       <c r="D161" s="9"/>
       <c r="E161" s="9"/>
@@ -10837,7 +10874,7 @@
       <c r="R161" s="9"/>
       <c r="S161" s="9"/>
     </row>
-    <row r="162" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C162" s="9"/>
       <c r="D162" s="9"/>
       <c r="E162" s="9"/>
@@ -10871,7 +10908,7 @@
       <c r="R162" s="9"/>
       <c r="S162" s="9"/>
     </row>
-    <row r="163" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="3:19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C163" s="9"/>
       <c r="D163" s="9"/>
       <c r="E163" s="9"/>
@@ -10919,10 +10956,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36FC5B27-9E4B-4195-A664-98F7198337D3}">
-  <dimension ref="A1:U14"/>
-  <sheetFormatPr defaultColWidth="14.625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U15"/>
+  <sheetFormatPr defaultColWidth="14.6640625" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3" t="s">
@@ -10951,7 +10988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
@@ -10989,7 +11026,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="3"/>
       <c r="D3" s="3" t="s">
         <v>15</v>
@@ -11025,7 +11062,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
@@ -11053,7 +11090,7 @@
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
     </row>
-    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C5" s="3"/>
       <c r="D5" s="3" t="s">
         <v>15</v>
@@ -11079,7 +11116,7 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
-    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
         <v>21</v>
       </c>
@@ -11110,7 +11147,7 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
@@ -11138,7 +11175,7 @@
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
     </row>
-    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -11167,7 +11204,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
@@ -11229,7 +11266,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>24</v>
       </c>
@@ -11291,7 +11328,7 @@
       </c>
       <c r="S11" s="3"/>
     </row>
-    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>135</v>
       </c>
@@ -11351,7 +11388,7 @@
       <c r="R12" s="9"/>
       <c r="S12" s="3"/>
     </row>
-    <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>9</v>
       </c>
@@ -11411,7 +11448,7 @@
       <c r="R13" s="9"/>
       <c r="S13" s="3"/>
     </row>
-    <row r="14" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>14</v>
       </c>
@@ -11468,6 +11505,67 @@
       <c r="Q14" s="23"/>
       <c r="R14" s="9"/>
       <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>50</v>
+      </c>
+      <c r="B15" s="3">
+        <v>60</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>497</v>
+      </c>
+      <c r="D15" s="30">
+        <v>3</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>496</v>
+      </c>
+      <c r="F15" s="30">
+        <v>14</v>
+      </c>
+      <c r="G15" s="30">
+        <v>13</v>
+      </c>
+      <c r="H15" s="30">
+        <v>9.5</v>
+      </c>
+      <c r="I15" s="17">
+        <f t="shared" ref="I15" si="11">(F15*$I$2)+(G15*$I$3)</f>
+        <v>34.5</v>
+      </c>
+      <c r="J15" s="9">
+        <f t="shared" ref="J15" si="12">(F15*$I$4)+(G15*$I$5)+(H15*$I$7)</f>
+        <v>13.5</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" ref="K15" si="13">I15+J15</f>
+        <v>48</v>
+      </c>
+      <c r="L15" s="11">
+        <f t="shared" ref="L15" si="14">H15*$M$2</f>
+        <v>59.375</v>
+      </c>
+      <c r="M15" s="11">
+        <f t="shared" ref="M15" si="15">H15*$M$3</f>
+        <v>14.25</v>
+      </c>
+      <c r="N15" s="9">
+        <v>1</v>
+      </c>
+      <c r="O15" s="9">
+        <v>1</v>
+      </c>
+      <c r="P15" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="Q15" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="R15" s="23" t="s">
+        <v>500</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -11479,15 +11577,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:U29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.875" customWidth="1"/>
+    <col min="1" max="1" width="23.88671875" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="21.25" customWidth="1"/>
+    <col min="9" max="9" width="21.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>34</v>
       </c>
@@ -11528,7 +11626,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>460</v>
       </c>
@@ -11565,7 +11663,7 @@
       <c r="L2" s="11"/>
       <c r="U2" s="24"/>
     </row>
-    <row r="3" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>461</v>
       </c>
@@ -11600,7 +11698,7 @@
       <c r="L3" s="11"/>
       <c r="U3" s="24"/>
     </row>
-    <row r="4" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>462</v>
       </c>
@@ -11634,7 +11732,7 @@
       <c r="L4" s="11"/>
       <c r="U4" s="24"/>
     </row>
-    <row r="5" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>446</v>
       </c>
@@ -11668,7 +11766,7 @@
       <c r="L5" s="11"/>
       <c r="U5" s="24"/>
     </row>
-    <row r="6" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>447</v>
       </c>
@@ -11702,7 +11800,7 @@
       <c r="L6" s="11"/>
       <c r="U6" s="24"/>
     </row>
-    <row r="7" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>448</v>
       </c>
@@ -11739,7 +11837,7 @@
       <c r="L7" s="11"/>
       <c r="U7" s="24"/>
     </row>
-    <row r="8" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>449</v>
       </c>
@@ -11775,7 +11873,7 @@
       </c>
       <c r="L8" s="11"/>
     </row>
-    <row r="9" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>450</v>
       </c>
@@ -11809,7 +11907,7 @@
       <c r="K9" s="11"/>
       <c r="L9" s="11"/>
     </row>
-    <row r="10" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>451</v>
       </c>
@@ -11843,7 +11941,7 @@
       <c r="K10" s="11"/>
       <c r="L10" s="11"/>
     </row>
-    <row r="11" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -11857,7 +11955,7 @@
       <c r="K11" s="11"/>
       <c r="L11" s="11"/>
     </row>
-    <row r="12" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="12"/>
@@ -11871,7 +11969,7 @@
       <c r="K12" s="11"/>
       <c r="L12" s="11"/>
     </row>
-    <row r="13" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12"/>
       <c r="B13" s="12"/>
       <c r="C13" s="12"/>
@@ -11885,7 +11983,7 @@
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
     </row>
-    <row r="14" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -11899,7 +11997,7 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
     </row>
-    <row r="15" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12"/>
       <c r="B15" s="12"/>
       <c r="C15" s="12"/>
@@ -11913,7 +12011,7 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
@@ -11927,7 +12025,7 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -11941,7 +12039,7 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -11955,7 +12053,7 @@
       <c r="K18" s="11"/>
       <c r="L18" s="11"/>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -11969,7 +12067,7 @@
       <c r="K19" s="11"/>
       <c r="L19" s="11"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -11983,7 +12081,7 @@
       <c r="K20" s="11"/>
       <c r="L20" s="11"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
@@ -11997,7 +12095,7 @@
       <c r="K21" s="11"/>
       <c r="L21" s="11"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
@@ -12011,7 +12109,7 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="22"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -12025,7 +12123,7 @@
       <c r="K23" s="11"/>
       <c r="L23" s="11"/>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -12039,7 +12137,7 @@
       <c r="K24" s="11"/>
       <c r="L24" s="11"/>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -12053,7 +12151,7 @@
       <c r="K25" s="11"/>
       <c r="L25" s="11"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -12067,7 +12165,7 @@
       <c r="K26" s="11"/>
       <c r="L26" s="11"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="21"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
@@ -12081,7 +12179,7 @@
       <c r="K27" s="11"/>
       <c r="L27" s="11"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -12095,7 +12193,7 @@
       <c r="K28" s="11"/>
       <c r="L28" s="11"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -12119,7 +12217,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12129,9 +12227,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="D5:S67"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="5" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="4:19" x14ac:dyDescent="0.25">
       <c r="F5" t="s">
         <v>256</v>
       </c>
@@ -12145,7 +12243,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="4:19" x14ac:dyDescent="0.25">
       <c r="F6" t="s">
         <v>260</v>
       </c>
@@ -12177,7 +12275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
         <v>264</v>
       </c>
@@ -12224,7 +12322,7 @@
         <v>6.4375</v>
       </c>
     </row>
-    <row r="8" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E8" t="s">
         <v>28</v>
       </c>
@@ -12264,7 +12362,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="4:19" x14ac:dyDescent="0.25">
       <c r="D10" t="s">
         <v>265</v>
       </c>
@@ -12315,7 +12413,7 @@
         <v>1.3283417475728154</v>
       </c>
     </row>
-    <row r="11" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E11" t="s">
         <v>28</v>
       </c>
@@ -12355,7 +12453,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="12" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E12" t="s">
         <v>266</v>
       </c>
@@ -12391,7 +12489,7 @@
         <v>-0.5</v>
       </c>
     </row>
-    <row r="13" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="4:19" x14ac:dyDescent="0.25">
       <c r="E13" t="s">
         <v>267</v>
       </c>
@@ -12430,7 +12528,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="4:19" x14ac:dyDescent="0.25">
       <c r="Q14">
         <f>Q13*$O$7</f>
         <v>12.5</v>
@@ -12440,13 +12538,13 @@
         <v>13.25</v>
       </c>
     </row>
-    <row r="15" spans="4:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="4:19" x14ac:dyDescent="0.25">
       <c r="Q15">
         <f>Q13*$O$8</f>
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q17">
         <f>Q13*$O$10</f>
         <v>16.8</v>
@@ -12460,18 +12558,18 @@
         <v>1.3135698113207548</v>
       </c>
     </row>
-    <row r="18" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q18">
         <f>Q13*$O$11</f>
         <v>1.8</v>
       </c>
     </row>
-    <row r="20" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q20" s="1">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q21">
         <f>Q20*$O$7</f>
         <v>31.25</v>
@@ -12481,13 +12579,13 @@
         <v>35.9375</v>
       </c>
     </row>
-    <row r="22" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q22">
         <f>Q20*$O$8</f>
         <v>7.5</v>
       </c>
     </row>
-    <row r="24" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q24">
         <f>Q20*$O$10</f>
         <v>42</v>
@@ -12501,18 +12599,18 @@
         <v>1.2738782608695653</v>
       </c>
     </row>
-    <row r="25" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q25">
         <f>Q20*$O$11</f>
         <v>4.5</v>
       </c>
     </row>
-    <row r="27" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q27" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q28">
         <f>Q27*$O$7</f>
         <v>62.5</v>
@@ -12522,13 +12620,13 @@
         <v>81.25</v>
       </c>
     </row>
-    <row r="29" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q29">
         <f>Q27*$O$8</f>
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q31">
         <f>Q27*$O$10</f>
         <v>84</v>
@@ -12542,18 +12640,18 @@
         <v>1.2199384615384614</v>
       </c>
     </row>
-    <row r="32" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q32">
         <f>Q27*$O$11</f>
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q34" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q35">
         <f>Q34*$O$7</f>
         <v>93.75</v>
@@ -12563,13 +12661,13 @@
         <v>135.9375</v>
       </c>
     </row>
-    <row r="36" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q36">
         <f>Q34*$O$8</f>
         <v>22.5</v>
       </c>
     </row>
-    <row r="38" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q38">
         <f>Q34*$O$10</f>
         <v>126</v>
@@ -12583,18 +12681,18 @@
         <v>1.1771586206896552</v>
       </c>
     </row>
-    <row r="39" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q39">
         <f>Q34*$O$11</f>
         <v>13.5</v>
       </c>
     </row>
-    <row r="41" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q41" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q42">
         <f>Q41*$O$7</f>
         <v>125</v>
@@ -12604,13 +12702,13 @@
         <v>200</v>
       </c>
     </row>
-    <row r="43" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q43">
         <f>Q41*$O$8</f>
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q45">
         <f>Q41*$O$10</f>
         <v>168</v>
@@ -12624,18 +12722,18 @@
         <v>1.1423999999999999</v>
       </c>
     </row>
-    <row r="46" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q46">
         <f>Q41*$O$11</f>
         <v>18</v>
       </c>
     </row>
-    <row r="48" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q48" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="49" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q49">
         <f>Q48*$O$7</f>
         <v>156.25</v>
@@ -12645,13 +12743,13 @@
         <v>273.4375</v>
       </c>
     </row>
-    <row r="50" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q50">
         <f>Q48*$O$8</f>
         <v>37.5</v>
       </c>
     </row>
-    <row r="52" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q52">
         <f>Q48*$O$10</f>
         <v>210</v>
@@ -12665,18 +12763,18 @@
         <v>1.1135999999999999</v>
       </c>
     </row>
-    <row r="53" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q53">
         <f>Q48*$O$11</f>
         <v>22.5</v>
       </c>
     </row>
-    <row r="55" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q55" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="56" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="56" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q56">
         <f>Q55*$O$7</f>
         <v>218.75</v>
@@ -12686,13 +12784,13 @@
         <v>448.43749999999994</v>
       </c>
     </row>
-    <row r="57" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="57" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q57">
         <f>Q55*$O$8</f>
         <v>52.5</v>
       </c>
     </row>
-    <row r="59" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q59">
         <f>Q55*$O$10</f>
         <v>294</v>
@@ -12706,18 +12804,18 @@
         <v>1.0686439024390244</v>
       </c>
     </row>
-    <row r="60" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q60">
         <f>Q55*$O$11</f>
         <v>31.5</v>
       </c>
     </row>
-    <row r="62" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q62" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="63" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q63">
         <f>Q62*$O$7</f>
         <v>250</v>
@@ -12727,13 +12825,13 @@
         <v>550</v>
       </c>
     </row>
-    <row r="64" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="64" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q64">
         <f>Q62*$O$8</f>
         <v>60</v>
       </c>
     </row>
-    <row r="66" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="66" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q66">
         <f>Q62*$O$10</f>
         <v>336</v>
@@ -12747,7 +12845,7 @@
         <v>1.0507636363636363</v>
       </c>
     </row>
-    <row r="67" spans="17:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="17:19" x14ac:dyDescent="0.25">
       <c r="Q67">
         <f>Q62*$O$11</f>
         <v>36</v>
